--- a/results/Int Task Remove ACC -0.7/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_5_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6296355998299353</v>
+        <v>0.6319461846665859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6004645102616011</v>
+        <v>0.6263405967468092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6014126771389715</v>
+        <v>0.6440154268933069</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6014126771389715</v>
+        <v>0.6281682992687782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6014126771389715</v>
+        <v>0.633428267339417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6029176368893933</v>
+        <v>0.633428267339417</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6417023783713773</v>
+        <v>0.6317202295309987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6371498399308479</v>
+        <v>0.6359338352681475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6544427988591026</v>
+        <v>0.6393970728603245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6436229970238683</v>
+        <v>0.6393970728603245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6210390979814675</v>
+        <v>0.6388402799872733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6245762461320141</v>
+        <v>0.6262666861884395</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6533359002587573</v>
+        <v>0.6260111668295045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6413338814446488</v>
+        <v>0.627319735667687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6469327822186682</v>
+        <v>0.6277111096720061</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6576853606412902</v>
+        <v>0.6340322221878089</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6646938413499306</v>
+        <v>0.6377185992752542</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6602690625888686</v>
+        <v>0.626204742101425</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6641518305885533</v>
+        <v>0.6276720426625821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6629171723087406</v>
+        <v>0.6282288355356334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6588689854403239</v>
+        <v>0.6216536114810549</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6433889469223644</v>
+        <v>0.6216536114810549</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6258580663871673</v>
+        <v>0.6181931895291968</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6285142710729561</v>
+        <v>0.6235203810124479</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6252449607077393</v>
+        <v>0.6246716259478149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.622890029536067</v>
+        <v>0.6307815654397044</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5921629467365321</v>
+        <v>0.6581224888007906</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5965285970508983</v>
+        <v>0.6552565189112483</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5929970801809894</v>
+        <v>0.6848070160125465</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5615421543590335</v>
+        <v>0.6733617900714891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5394101655878072</v>
+        <v>0.6730080752564345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5394101655878072</v>
+        <v>0.6630973732891465</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5364984415430836</v>
+        <v>0.6629910828671102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5410643542751274</v>
+        <v>0.6609669894329019</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.524328188219924</v>
+        <v>0.6688226259224741</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4962949692954423</v>
+        <v>0.6720732826705785</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4956628580438621</v>
+        <v>0.6796733998012158</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5164781830109895</v>
+        <v>0.6797110589904802</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5085324460312142</v>
+        <v>0.676611038999434</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5124986273753446</v>
+        <v>0.6785450319434394</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5118503261919309</v>
+        <v>0.6752190568168059</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5172084897186894</v>
+        <v>0.6718635174668247</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5134763584760629</v>
+        <v>0.6562219315855715</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5070866147274883</v>
+        <v>0.714695037997066</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5077792622459236</v>
+        <v>0.685331429021931</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5077792622459236</v>
+        <v>0.7023459915136601</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5223030389205962</v>
+        <v>0.6941904893301309</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5219116649162769</v>
+        <v>0.6632244290585343</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5068339110088721</v>
+        <v>0.6583963098217982</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5673230158886583</v>
+        <v>0.6485084849321008</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5316291435666842</v>
+        <v>0.6287300195123875</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5274693869506334</v>
+        <v>0.6489132332279345</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5520073403743112</v>
+        <v>0.6268097528149363</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5221003128176395</v>
+        <v>0.601085710906946</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5442520110710978</v>
+        <v>0.5875653580509012</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5016302557446102</v>
+        <v>0.6009632305530762</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5029469195487092</v>
+        <v>0.6141340920545446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5029845787379736</v>
+        <v>0.6105297204913855</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5064224755672811</v>
+        <v>0.6044989708834635</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5094112777657331</v>
+        <v>0.5830529424849151</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5102249978178788</v>
+        <v>0.5916536677938613</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5091423841152836</v>
+        <v>0.5842041874202822</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4998933576229239</v>
+        <v>0.5301966865544728</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4995019836186047</v>
+        <v>0.5287107323762034</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5044634938154461</v>
+        <v>0.5262804828260018</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5017143729991356</v>
+        <v>0.5155145301118653</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.472274037825312</v>
+        <v>0.5114205890882675</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4703305420952306</v>
+        <v>0.5065977491771291</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4706641954730135</v>
+        <v>0.5125288955087721</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4876840372903404</v>
+        <v>0.5156732618348402</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4956054893723656</v>
+        <v>0.5156356026455756</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4865246973890567</v>
+        <v>0.5156356026455756</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.491233503867282</v>
+        <v>0.5131018783136567</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4930545192434937</v>
+        <v>0.5052624317559178</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4930545192434937</v>
+        <v>0.48352322480917</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4940780044993932</v>
+        <v>0.4821097733691108</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4940780044993932</v>
+        <v>0.479838255541884</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4993312854242747</v>
+        <v>0.479838255541884</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4952964728473726</v>
+        <v>0.4757066553290217</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4948955960569773</v>
+        <v>0.4656305344930017</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4831462809614849</v>
+        <v>0.4659089309295273</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5320321320873187</v>
+        <v>0.4715078317035468</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5325364836594314</v>
+        <v>0.4892002596020374</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.52024938126304</v>
+        <v>0.4973652645716425</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5217972795283239</v>
+        <v>0.4975912197072297</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4732859085648963</v>
+        <v>0.4975912197072297</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4875112273657714</v>
+        <v>0.498148012580281</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4803602048659896</v>
+        <v>0.4972227227805011</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4985027832604552</v>
+        <v>0.4985246044729262</v>
       </c>
     </row>
   </sheetData>
